--- a/experiment/HAT_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/HAT_bestx4/Test/results-Set5/Set5.xlsx
@@ -455,7 +455,7 @@
         <v>33.76</v>
       </c>
       <c r="C2" t="n">
-        <v>0.894</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.82</v>
+        <v>34.93</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9412</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.77</v>
+        <v>28.85</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9196</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>32.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0.798</v>
+        <v>0.7981</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.77</v>
+        <v>30.82</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9146</v>
+        <v>0.9153</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.22</v>
+        <v>32.27</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8935</v>
+        <v>0.8941</v>
       </c>
     </row>
   </sheetData>
